--- a/config/Config/Data/局内成长.xlsx
+++ b/config/Config/Data/局内成长.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="373">
   <si>
     <t>##var</t>
   </si>
@@ -186,7 +186,7 @@
     <t>顺手家伙</t>
   </si>
   <si>
-    <t>普通近战，伤害稳定</t>
+    <t>街上抄的普通近战，稳，但不酷。</t>
   </si>
   <si>
     <t>Normal</t>
@@ -198,10 +198,10 @@
     <t>equip_pierce</t>
   </si>
   <si>
-    <t>竹竿一捅</t>
-  </si>
-  <si>
-    <t>直线贯穿，第二个目标承受较低伤害</t>
+    <t>晾衣竿一捅</t>
+  </si>
+  <si>
+    <t>直线贯穿，第二个倒霉蛋少挨一点。</t>
   </si>
   <si>
     <t>Pierce</t>
@@ -213,10 +213,10 @@
     <t>equip_chain</t>
   </si>
   <si>
-    <t>电线乱搭</t>
-  </si>
-  <si>
-    <t>攻击在邻近敌人之间弹跳</t>
+    <t>私拉电线</t>
+  </si>
+  <si>
+    <t>攻击在邻近敌人之间乱蹦。</t>
   </si>
   <si>
     <t>Chain</t>
@@ -231,7 +231,7 @@
     <t>工地抡锤</t>
   </si>
   <si>
-    <t>命中位置产生范围溅射</t>
+    <t>砸哪儿溅哪儿，安全帽警告已经响了。</t>
   </si>
   <si>
     <t>Splash</t>
@@ -297,10 +297,10 @@
     <t>Stat</t>
   </si>
   <si>
-    <t>加餐练功</t>
-  </si>
-  <si>
-    <t>随机一人攻击+1.5</t>
+    <t>多吃一碗拌粉</t>
+  </si>
+  <si>
+    <t>随机一人攻击+1.5，米粉才是力量。</t>
   </si>
   <si>
     <t>atk</t>
@@ -309,10 +309,10 @@
     <t>reward_hp</t>
   </si>
   <si>
-    <t>多睡一觉</t>
-  </si>
-  <si>
-    <t>随机一人生命上限+8</t>
+    <t>中午补觉成功</t>
+  </si>
+  <si>
+    <t>随机一人生命上限+8，眼袋退一点。</t>
   </si>
   <si>
     <t>hp</t>
@@ -324,10 +324,10 @@
     <t>Recovery</t>
   </si>
   <si>
-    <t>创可贴</t>
-  </si>
-  <si>
-    <t>全体现役回复30%</t>
+    <t>三块钱创口贴</t>
+  </si>
+  <si>
+    <t>全体现役回复30%，药店最便宜那款。</t>
   </si>
   <si>
     <t>heal</t>
@@ -339,10 +339,10 @@
     <t>TeamBuff</t>
   </si>
   <si>
-    <t>壮胆</t>
-  </si>
-  <si>
-    <t>下一波全队攻击+15%</t>
+    <t>课间壮胆</t>
+  </si>
+  <si>
+    <t>下一波全队攻击+15%，先吹再打。</t>
   </si>
   <si>
     <t>reward_campus</t>
@@ -351,10 +351,10 @@
     <t>CampusSkill</t>
   </si>
   <si>
-    <t>校园技</t>
-  </si>
-  <si>
-    <t>随机一人校园技+1</t>
+    <t>课间绝活+1</t>
+  </si>
+  <si>
+    <t>随机一人课间绝活升级。学校那点事。</t>
   </si>
   <si>
     <t>reward_job</t>
@@ -363,10 +363,10 @@
     <t>JobSkill</t>
   </si>
   <si>
-    <t>就业技强化</t>
-  </si>
-  <si>
-    <t>已毕业兄弟就业技+1</t>
+    <t>工牌绝活进修</t>
+  </si>
+  <si>
+    <t>已毕业兄弟的工牌绝活+1。没毕业的看着。</t>
   </si>
   <si>
     <t>reward_encounter</t>
@@ -375,10 +375,10 @@
     <t>Encounter</t>
   </si>
   <si>
-    <t>碰见老熟人</t>
-  </si>
-  <si>
-    <t>与一位兄弟增加好感，满后集合</t>
+    <t>巷口撞见熟人</t>
+  </si>
+  <si>
+    <t>跟一位兄弟熟络一点，满了才肯入队。</t>
   </si>
   <si>
     <t>reward_pierce</t>
@@ -387,19 +387,19 @@
     <t>Equipment</t>
   </si>
   <si>
-    <t>替换团队攻击核心：直线贯穿</t>
+    <t>替换团队攻击核心：直线贯穿，隔壁也能挨一下。</t>
   </si>
   <si>
     <t>reward_chain</t>
   </si>
   <si>
-    <t>替换团队攻击核心：弹跳连锁</t>
+    <t>替换团队攻击核心：弹跳连锁，电工看了会沉默。</t>
   </si>
   <si>
     <t>reward_splash</t>
   </si>
   <si>
-    <t>替换团队攻击核心：范围溅射</t>
+    <t>替换团队攻击核心：范围溅射，安全员已经在喊。</t>
   </si>
   <si>
     <t>reward_stone</t>
@@ -408,10 +408,10 @@
     <t>LootSkill</t>
   </si>
   <si>
-    <t>捡块石头</t>
-  </si>
-  <si>
-    <t>随机一人临时技能替换为飞石</t>
+    <t>捡块龙翔石</t>
+  </si>
+  <si>
+    <t>随机一人地摊技换成龙翔飞石。</t>
   </si>
   <si>
     <t>loot_stone_throw</t>
@@ -420,10 +420,10 @@
     <t>reward_cheer</t>
   </si>
   <si>
-    <t>一起吆喝</t>
-  </si>
-  <si>
-    <t>随机一人临时技能替换为组队壮胆</t>
+    <t>兄弟们上啊</t>
+  </si>
+  <si>
+    <t>随机一人地摊技换成现场加油。</t>
   </si>
   <si>
     <t>loot_group_cheer</t>
@@ -432,10 +432,10 @@
     <t>reward_first_aid</t>
   </si>
   <si>
-    <t>临时急救包</t>
-  </si>
-  <si>
-    <t>随机一人临时技能替换为急救</t>
+    <t>创口贴急救包</t>
+  </si>
+  <si>
+    <t>随机一人地摊技换成三块钱创口贴。</t>
   </si>
   <si>
     <t>loot_first_aid</t>
@@ -447,10 +447,10 @@
     <t>Event</t>
   </si>
   <si>
-    <t>龙南有状况</t>
-  </si>
-  <si>
-    <t>触发一件受派系影响的局内事件</t>
+    <t>龙南又出状况</t>
+  </si>
+  <si>
+    <t>触发一件看阵容的局内糗事，对口派系更好收场。</t>
   </si>
   <si>
     <t>required_tag</t>
@@ -504,22 +504,22 @@
     <t>event_shop_credit</t>
   </si>
   <si>
-    <t>小卖部赊账</t>
-  </si>
-  <si>
-    <t>老板拿出记账本，问谁能周转一下。</t>
+    <t>小卖部又翻账本</t>
+  </si>
+  <si>
+    <t>老板掏出那本油乎乎的本子：上周冰棍，谁家娃还没结？</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>账算清了，还攒下一点人情。</t>
+    <t>银行兄弟把账抹平了，还顺手攒点人情。</t>
   </si>
   <si>
     <t>AddFavor</t>
   </si>
   <si>
-    <t>先吃再说，大家恢复一点。</t>
+    <t>先吃后算，大家舔根冰棍回血。</t>
   </si>
   <si>
     <t>HealTeam</t>
@@ -528,22 +528,22 @@
     <t>event_teacher_check</t>
   </si>
   <si>
-    <t>老班查寝</t>
-  </si>
-  <si>
-    <t>脚步声已经到门口，谁来稳住场面？</t>
+    <t>老班手电筒来了</t>
+  </si>
+  <si>
+    <t>走廊灯一亮，脚步已经到床沿。谁来对答如流？</t>
   </si>
   <si>
     <t>Academic</t>
   </si>
   <si>
-    <t>对答如流，下一波士气大振。</t>
+    <t>学霸顶上，下一波全队像刚考完满分。</t>
   </si>
   <si>
     <t>NextWaveAtk</t>
   </si>
   <si>
-    <t>翻窗时摔了一跤。</t>
+    <t>翻窗时磕到膝盖，全队哎哟一声。</t>
   </si>
   <si>
     <t>DamageTeam</t>
@@ -552,172 +552,172 @@
     <t>event_night_blackout</t>
   </si>
   <si>
-    <t>夜市停电</t>
-  </si>
-  <si>
-    <t>摊位一片漆黑，线头还在冒火花。</t>
+    <t>烤串翻面灯灭了</t>
+  </si>
+  <si>
+    <t>夜市正香，摊位一片黑，线头还在冒火花。</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>供电恢复，下一波带电开打。</t>
-  </si>
-  <si>
-    <t>摸黑吃串，勉强回血。</t>
+    <t>能源兄弟把电送回来，下一波带电开打。</t>
+  </si>
+  <si>
+    <t>摸黑把串吃了，也算回血。</t>
   </si>
   <si>
     <t>event_rain_flood</t>
   </si>
   <si>
-    <t>雨天积水</t>
-  </si>
-  <si>
-    <t>路口水越涨越高，车都快熄火了。</t>
+    <t>路口变成游泳池</t>
+  </si>
+  <si>
+    <t>水已经漫过鞋面，电动车开始喝水。</t>
   </si>
   <si>
     <t>Civil</t>
   </si>
   <si>
-    <t>排水打通，下一波全队带护盾。</t>
+    <t>土木把排水打通，下一波全队踩着盾上场。</t>
   </si>
   <si>
     <t>NextWaveShield</t>
   </si>
   <si>
-    <t>趟水过去，大家损失一点血。</t>
+    <t>趟水过去，裤脚和血条一起湿。</t>
   </si>
   <si>
     <t>event_stalled_car</t>
   </si>
   <si>
-    <t>车趴窝了</t>
-  </si>
-  <si>
-    <t>路边车打不着火，围了一圈人。</t>
+    <t>路边车装死</t>
+  </si>
+  <si>
+    <t>打不着火，围了一圈指挥的，没一个会修。</t>
   </si>
   <si>
     <t>Mechanical</t>
   </si>
   <si>
-    <t>三两下修好，下一波火力提升。</t>
-  </si>
-  <si>
-    <t>推车也算锻炼，恢复一点。</t>
+    <t>机械兄弟两下搞定，下一波火力上涨。</t>
+  </si>
+  <si>
+    <t>推车也算锻炼，喘匀了回一点血。</t>
   </si>
   <si>
     <t>event_industrial_shift</t>
   </si>
   <si>
-    <t>工业园赶订单</t>
-  </si>
-  <si>
-    <t>新项目不断落地，设备、资金和程序都缺人。</t>
-  </si>
-  <si>
-    <t>设备顺利开线，下一波火力提升。</t>
-  </si>
-  <si>
-    <t>赶工出岔子，大家掉了一点血。</t>
+    <t>工业园又赶单</t>
+  </si>
+  <si>
+    <t>新项目落地，设备、资金、程序同时缺人。</t>
+  </si>
+  <si>
+    <t>线开起来了，下一波打得更狠。</t>
+  </si>
+  <si>
+    <t>赶工出岔，全队被进度条抽了一下。</t>
   </si>
   <si>
     <t>event_leave_hometown</t>
   </si>
   <si>
-    <t>毕业后各奔东西</t>
-  </si>
-  <si>
-    <t>有人上大学，有人复读，也有人先去工作。</t>
-  </si>
-  <si>
-    <t>学霸整理路线，随机兄弟好感增加。</t>
+    <t>站台上各奔东西</t>
+  </si>
+  <si>
+    <t>有人上学，有人复读，有人先去打工。票根还热。</t>
+  </si>
+  <si>
+    <t>学霸把路线讲明白，随机兄弟更熟一分。</t>
   </si>
   <si>
     <t>AddAffinity</t>
   </si>
   <si>
-    <t>临走前吃顿饭，大家恢复一点。</t>
+    <t>临走前先干一碗粉，大家回血。</t>
   </si>
   <si>
     <t>event_hsr_construction</t>
   </si>
   <si>
-    <t>高铁工地赶进度</t>
-  </si>
-  <si>
-    <t>桥隧和设备同时催进度。</t>
-  </si>
-  <si>
-    <t>施工组织顺畅，下一波全队带盾。</t>
-  </si>
-  <si>
-    <t>绕路赶场，大家受到一点损耗。</t>
+    <t>高铁工地催进度</t>
+  </si>
+  <si>
+    <t>桥隧和设备一起喊赶，安全帽满天飞。</t>
+  </si>
+  <si>
+    <t>施工组织顺了，下一波全队带盾。</t>
+  </si>
+  <si>
+    <t>绕路赶场，全队被晒掉一层血。</t>
   </si>
   <si>
     <t>event_tourism_festival</t>
   </si>
   <si>
-    <t>围屋旅游文化节</t>
-  </si>
-  <si>
-    <t>游客潮、米酒摊和舞台节目一起开场。</t>
+    <t>围屋米酒摊开战</t>
+  </si>
+  <si>
+    <t>游客、米酒、舞台节目同时开场，摊主已经在喊人。</t>
   </si>
   <si>
     <t>Startup</t>
   </si>
   <si>
-    <t>摊位经营得当，赚到人情。</t>
-  </si>
-  <si>
-    <t>帮忙收摊，大家吃饱恢复。</t>
+    <t>创业兄弟把摊盘活，人情进账。</t>
+  </si>
+  <si>
+    <t>帮忙收摊，好在酒酿让大家回血。</t>
   </si>
   <si>
     <t>event_graduation_split</t>
   </si>
   <si>
-    <t>毕业季分流</t>
-  </si>
-  <si>
-    <t>工作、考研、考公同时摆在面前。</t>
-  </si>
-  <si>
-    <t>资料共享，随机兄弟好感增加。</t>
-  </si>
-  <si>
-    <t>先聚一顿，下一波壮胆。</t>
+    <t>毕业季三岔口</t>
+  </si>
+  <si>
+    <t>工作、考研、考公三张表拍在桌上，先选哪个？</t>
+  </si>
+  <si>
+    <t>资料一共享，随机兄弟好感上涨。</t>
+  </si>
+  <si>
+    <t>想不通就先聚一顿，下一波壮胆。</t>
   </si>
   <si>
     <t>event_county_to_city</t>
   </si>
   <si>
-    <t>撤县设市新机会</t>
-  </si>
-  <si>
-    <t>开发建设、公共服务和商业机会同时涌来。</t>
+    <t>撤县设市的饼</t>
+  </si>
+  <si>
+    <t>建设、公服、商机一起涌来，窗口已经排到门口。</t>
   </si>
   <si>
     <t>Official</t>
   </si>
   <si>
-    <t>手续和资源顺利对接，声势转成人情。</t>
-  </si>
-  <si>
-    <t>建设阵痛袭来，全队先顶一层盾。</t>
+    <t>公职兄弟把手续走通，声势变成人情。</t>
+  </si>
+  <si>
+    <t>建设阵痛先到，全队顶一层盾挨过去。</t>
   </si>
   <si>
     <t>event_return_home_tide</t>
   </si>
   <si>
-    <t>龙南东站返乡潮</t>
-  </si>
-  <si>
-    <t>高铁到站，过年回来的兄弟越来越多。</t>
-  </si>
-  <si>
-    <t>接站安排顺畅，随机兄弟好感增加。</t>
-  </si>
-  <si>
-    <t>挤在人潮里，但团聚让大家恢复。</t>
+    <t>龙南东站人潮</t>
+  </si>
+  <si>
+    <t>高铁一停，过年回来的人把出站口堵成菜市场。</t>
+  </si>
+  <si>
+    <t>接站安排清楚，随机兄弟更熟。</t>
+  </si>
+  <si>
+    <t>挤成肉饼，但团聚让大家回了点血。</t>
   </si>
   <si>
     <t>role_id</t>
@@ -778,6 +778,9 @@
   </si>
   <si>
     <t>Bus_longtou</t>
+  </si>
+  <si>
+    <t>TM_PaoPao</t>
   </si>
   <si>
     <t>anchor_year</t>
@@ -1775,10 +1778,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2010,10 +2013,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2616,10 +2619,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3131,7 +3134,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3463,6 +3466,23 @@
       </c>
       <c r="F17">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -3484,58 +3504,58 @@
         <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
         <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -3564,19 +3584,19 @@
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
       </c>
       <c r="M2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N2" t="s">
         <v>11</v>
@@ -3588,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="Q2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R2" t="s">
         <v>11</v>
@@ -3597,7 +3617,7 @@
         <v>11</v>
       </c>
       <c r="T2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -3608,58 +3628,58 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -3667,7 +3687,7 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4">
         <v>1997</v>
@@ -3676,13 +3696,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -3691,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -3706,16 +3726,16 @@
         <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S4" t="s">
         <v>24</v>
@@ -3729,7 +3749,7 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C5">
         <v>2013</v>
@@ -3738,13 +3758,13 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H5" t="s">
         <v>29</v>
@@ -3753,10 +3773,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L5">
         <v>1.8</v>
@@ -3765,22 +3785,22 @@
         <v>196</v>
       </c>
       <c r="N5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q5" t="s">
         <v>226</v>
       </c>
       <c r="R5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -3791,7 +3811,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6">
         <v>2015</v>
@@ -3800,13 +3820,13 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -3815,10 +3835,10 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6">
         <v>1.7</v>
@@ -3827,19 +3847,19 @@
         <v>201</v>
       </c>
       <c r="N6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S6" t="s">
         <v>24</v>
@@ -3853,7 +3873,7 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C7">
         <v>2016</v>
@@ -3862,13 +3882,13 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
@@ -3877,10 +3897,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -3889,22 +3909,22 @@
         <v>207</v>
       </c>
       <c r="N7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -3915,7 +3935,7 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8">
         <v>2017</v>
@@ -3924,13 +3944,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H8" t="s">
         <v>31</v>
@@ -3939,10 +3959,10 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L8">
         <v>1.7</v>
@@ -3951,22 +3971,22 @@
         <v>212</v>
       </c>
       <c r="N8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -3977,7 +3997,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C9">
         <v>2019</v>
@@ -3986,13 +4006,13 @@
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H9" t="s">
         <v>33</v>
@@ -4001,10 +4021,10 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L9">
         <v>1.9</v>
@@ -4013,22 +4033,22 @@
         <v>218</v>
       </c>
       <c r="N9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -4039,7 +4059,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C10">
         <v>2020</v>
@@ -4048,13 +4068,13 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -4063,10 +4083,10 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L10">
         <v>1.8</v>
@@ -4075,22 +4095,22 @@
         <v>223</v>
       </c>
       <c r="N10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q10" t="s">
         <v>226</v>
       </c>
       <c r="R10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -4101,7 +4121,7 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C11">
         <v>2021</v>
@@ -4110,13 +4130,13 @@
         <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -4125,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -4137,22 +4157,22 @@
         <v>229</v>
       </c>
       <c r="N11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q11" t="s">
         <v>226</v>
       </c>
       <c r="R11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T11" t="b">
         <v>1</v>

--- a/config/Config/Data/局内成长.xlsx
+++ b/config/Config/Data/局内成长.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="370">
   <si>
     <t>##var</t>
   </si>
@@ -609,13 +609,13 @@
     <t>event_industrial_shift</t>
   </si>
   <si>
-    <t>工业园又赶单</t>
-  </si>
-  <si>
-    <t>新项目落地，设备、资金、程序同时缺人。</t>
-  </si>
-  <si>
-    <t>线开起来了，下一波打得更狠。</t>
+    <t>网吧包夜还在赶单</t>
+  </si>
+  <si>
+    <t>包夜到一半，机房风扇罢工，进度条还在转。谁去接线？</t>
+  </si>
+  <si>
+    <t>线接上了，下一波开黑开得更狠。</t>
   </si>
   <si>
     <t>赶工出岔，全队被进度条抽了一下。</t>
@@ -624,10 +624,10 @@
     <t>event_leave_hometown</t>
   </si>
   <si>
-    <t>站台上各奔东西</t>
-  </si>
-  <si>
-    <t>有人上学，有人复读，有人先去打工。票根还热。</t>
+    <t>站台上先演离乡</t>
+  </si>
+  <si>
+    <t>分数没出，黄牛先走。有人上学，有人复读，有人去当网管。</t>
   </si>
   <si>
     <t>学霸把路线讲明白，随机兄弟更熟一分。</t>
@@ -636,19 +636,19 @@
     <t>AddAffinity</t>
   </si>
   <si>
-    <t>临走前先干一碗粉，大家回血。</t>
+    <t>票没抢到，先干一碗粉回血。</t>
   </si>
   <si>
     <t>event_hsr_construction</t>
   </si>
   <si>
-    <t>高铁工地催进度</t>
-  </si>
-  <si>
-    <t>桥隧和设备一起喊赶，安全帽满天飞。</t>
-  </si>
-  <si>
-    <t>施工组织顺了，下一波全队带盾。</t>
+    <t>光缆被挖，段位也掉</t>
+  </si>
+  <si>
+    <t>景观大道开挖，宿舍网先祭天。段位还在掉。</t>
+  </si>
+  <si>
+    <t>光缆接上了，下一波全队带盾。</t>
   </si>
   <si>
     <t>绕路赶场，全队被晒掉一层血。</t>
@@ -657,10 +657,10 @@
     <t>event_tourism_festival</t>
   </si>
   <si>
-    <t>围屋米酒摊开战</t>
-  </si>
-  <si>
-    <t>游客、米酒、舞台节目同时开场，摊主已经在喊人。</t>
+    <t>围屋空投先落地</t>
+  </si>
+  <si>
+    <t>空投砸在土楼顶上，米酒当急救包，摊主已经在喊人。</t>
   </si>
   <si>
     <t>Startup</t>
@@ -675,10 +675,10 @@
     <t>event_graduation_split</t>
   </si>
   <si>
-    <t>毕业季三岔口</t>
-  </si>
-  <si>
-    <t>工作、考研、考公三张表拍在桌上，先选哪个？</t>
+    <t>合同和志愿一起拍桌上</t>
+  </si>
+  <si>
+    <t>桌上三张纸：考研、考公、热爱游戏的加班合同。先点哪个？</t>
   </si>
   <si>
     <t>资料一共享，随机兄弟好感上涨。</t>
@@ -690,10 +690,10 @@
     <t>event_county_to_city</t>
   </si>
   <si>
-    <t>撤县设市的饼</t>
-  </si>
-  <si>
-    <t>建设、公服、商机一起涌来，窗口已经排到门口。</t>
+    <t>窗口排队领 404</t>
+  </si>
+  <si>
+    <t>窗口在发数字市民码，扫开 404。剪彩的横幅比服务器先到。</t>
   </si>
   <si>
     <t>Official</t>
@@ -708,10 +708,10 @@
     <t>event_return_home_tide</t>
   </si>
   <si>
-    <t>龙南东站人潮</t>
-  </si>
-  <si>
-    <t>高铁一停，过年回来的人把出站口堵成菜市场。</t>
+    <t>回村先给冰柜充值</t>
+  </si>
+  <si>
+    <t>人挤回来了。冰柜旁挂着充值，抢的是包间和充电宝。</t>
   </si>
   <si>
     <t>接站安排清楚，随机兄弟更熟。</t>
@@ -900,40 +900,40 @@
     <t>cohort_1997</t>
   </si>
   <si>
-    <t>97届兄弟出生年</t>
-  </si>
-  <si>
-    <t>这批兄弟大多出生于1997年前后。</t>
-  </si>
-  <si>
-    <t>作为共同纪年原点，不严格限制技能获得年份。</t>
+    <t>小卖部开始租卡带</t>
+  </si>
+  <si>
+    <t>97届还没站齐，柜台已经在数红白机卡带。通关的请辣条，没通的扫巷子。</t>
+  </si>
+  <si>
+    <t>共同纪年原点。波间当「从同一条巷子出门」，不卡就业技年份。</t>
   </si>
   <si>
     <t>Cohort</t>
   </si>
   <si>
-    <t>从同一座小城出发。</t>
-  </si>
-  <si>
-    <t>个人月份与年份可能前后浮动。</t>
+    <t>从同一座小城、同一台游戏机出发。</t>
+  </si>
+  <si>
+    <t>谁家先租到卡带，月份可以瞎编。</t>
   </si>
   <si>
     <t>Oral</t>
   </si>
   <si>
-    <t>兄弟口述</t>
+    <t>兄弟口述·卡带纪年</t>
   </si>
   <si>
     <t>economy_zone_2013</t>
   </si>
   <si>
-    <t>龙南经开区升级</t>
-  </si>
-  <si>
-    <t>2013年3月，龙南经开区升格为国家级经济技术开发区。</t>
-  </si>
-  <si>
-    <t>工业园订单、开发建设与就业机会同时增加。</t>
+    <t>工业园外开了通宵网吧</t>
+  </si>
+  <si>
+    <t>园里白班拧螺丝，园外通宵打页游。有人说这叫产业升级，有人说这叫包夜。</t>
+  </si>
+  <si>
+    <t>赶工单和开黑房同时进波间池。机械、互联网兄弟更容易撞见。</t>
   </si>
   <si>
     <t>Industry</t>
@@ -945,55 +945,58 @@
     <t>industrial_park</t>
   </si>
   <si>
-    <t>机械、互联网、银行、创业类兄弟更容易出现。</t>
-  </si>
-  <si>
-    <t>赶工、设备故障和经营风险同步增加。</t>
-  </si>
-  <si>
-    <t>龙南市人民政府·市情简介</t>
-  </si>
-  <si>
-    <t>http://www.jxln.gov.cn/lnzf/c103680/202308/f05e9c5bdbba43b1a65954a38ff99ac8.shtml</t>
+    <t>机械、互联网、银行、创业类更容易出现——有人接单，有人充点卡。</t>
+  </si>
+  <si>
+    <t>风扇一停，下一波怪会带着进度条冲过来。</t>
+  </si>
+  <si>
+    <t>Creative</t>
+  </si>
+  <si>
+    <t>玩法创作·网吧年鉴</t>
   </si>
   <si>
     <t>cohort_2015</t>
   </si>
   <si>
-    <t>2015毕业与离乡</t>
-  </si>
-  <si>
-    <t>多数兄弟于2015年前后高中毕业，升学或复读。</t>
-  </si>
-  <si>
-    <t>解锁大学、复读和提前就业的分流。</t>
+    <t>分数没出，火车票先黄了</t>
+  </si>
+  <si>
+    <t>高考刚完，站台已经在演「我去大城市做游戏」。分数线还在路上，行李已经过安检。</t>
+  </si>
+  <si>
+    <t>离乡分流：大学、复读、先去当网管。波间可遇外地同学。</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Academic|Civil|Internet|Startup</t>
+    <t>Academic|Official|Internet|Startup</t>
   </si>
   <si>
     <t>station_home</t>
   </si>
   <si>
-    <t>同学关系延伸到不同学校和行业。</t>
-  </si>
-  <si>
-    <t>分隔异地，好感增长节奏变慢。</t>
+    <t>同学关系扩到不同机房和不同城市。</t>
+  </si>
+  <si>
+    <t>人已分开，好感长得慢。</t>
+  </si>
+  <si>
+    <t>兄弟口述·站台话</t>
   </si>
   <si>
     <t>hsr_build_2016</t>
   </si>
   <si>
-    <t>赣深高铁建设</t>
-  </si>
-  <si>
-    <t>2016年赣深高铁开工建设，龙南迎来高铁建设期。</t>
-  </si>
-  <si>
-    <t>工地、运输和设备事件增多。</t>
+    <t>景观大道把光缆挖断了</t>
+  </si>
+  <si>
+    <t>县城修景观大道，宿舍网先祭天。同一周王者开服，段位和路面一起翻修。</t>
+  </si>
+  <si>
+    <t>施工与掉线事件增多。土木、机械相遇加权。</t>
   </si>
   <si>
     <t>Transport</t>
@@ -1008,28 +1011,22 @@
     <t>土木与机械兄弟相遇概率提高。</t>
   </si>
   <si>
-    <t>施工期道路、噪声与赶工形成额外敌潮。</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>龙南全域旅游与高铁建设报道</t>
-  </si>
-  <si>
-    <t>http://www.tourjie.com/article/1855.html</t>
+    <t>掉线和绕路一起上场，波次更挤。</t>
+  </si>
+  <si>
+    <t>玩法创作·断网纪年</t>
   </si>
   <si>
     <t>tourism_festival_2017</t>
   </si>
   <si>
-    <t>围美龙南旅游文化节</t>
-  </si>
-  <si>
-    <t>2017年起，龙南持续举办“围美龙南·客迎天下”旅游文化节。</t>
-  </si>
-  <si>
-    <t>围屋游客潮、米酒摊和舞台事件进入奖励池。</t>
+    <t>围屋被改成落地岛</t>
+  </si>
+  <si>
+    <t>游客还没到，吃鸡空投先到。米酒当急救包，土楼当盒子。</t>
+  </si>
+  <si>
+    <t>围屋游客潮、米酒救急包和空投事件进奖励池。</t>
   </si>
   <si>
     <t>Culture</t>
@@ -1041,28 +1038,25 @@
     <t>guanxi_wei</t>
   </si>
   <si>
-    <t>创业、烟草和学术类兄弟更易出现。</t>
-  </si>
-  <si>
-    <t>人潮、临时摊位和舞台事故提升波次密度。</t>
-  </si>
-  <si>
-    <t>中国江西网·围美龙南客迎天下</t>
-  </si>
-  <si>
-    <t>https://jxgz.jxnews.com.cn/system/2020/01/08/018717283.shtml</t>
+    <t>创业、烟草和学术类更易出现。</t>
+  </si>
+  <si>
+    <t>人潮、临时摊和成盒事故抬高波次密度。</t>
+  </si>
+  <si>
+    <t>玩法创作·成盒文化节</t>
   </si>
   <si>
     <t>graduation_2019</t>
   </si>
   <si>
-    <t>大学毕业与世客会申办</t>
-  </si>
-  <si>
-    <t>多数兄弟于2019年前后毕业；同年龙南获得第32届世客会举办权。</t>
-  </si>
-  <si>
-    <t>正式分流工作、考研、考公，并强化返乡联系。</t>
+    <t>第一份游戏民工合同</t>
+  </si>
+  <si>
+    <t>offer 写着热爱游戏，附件是无尽加班。有人考研，有人考公，有人点了同意并继续加班。</t>
+  </si>
+  <si>
+    <t>正式分流工作、考研、考公。波间见到带着 offer 的人。</t>
   </si>
   <si>
     <t>Academic|Official|Finance|Startup|Internet</t>
@@ -1071,25 +1065,22 @@
     <t>各行业兄弟开始带着就业技能回到队伍。</t>
   </si>
   <si>
-    <t>考试延期与求职失败会推迟就业技。</t>
-  </si>
-  <si>
-    <t>客家摇篮网·龙南获世客会承办权</t>
-  </si>
-  <si>
-    <t>http://www.gnhakka.com/n489/c196658/content.html</t>
+    <t>考试延期与求职失败仍会推迟就业技，大事件只改相遇。</t>
+  </si>
+  <si>
+    <t>玩法创作·合同纪年</t>
   </si>
   <si>
     <t>city_2020</t>
   </si>
   <si>
-    <t>龙南撤县设市</t>
-  </si>
-  <si>
-    <t>2020年6月，龙南撤县设市。</t>
-  </si>
-  <si>
-    <t>城市开发、公共服务和商业机会并存。</t>
+    <t>电竞一条街还在 PPT 里</t>
+  </si>
+  <si>
+    <t>广场剪了彩，服务器没到。窗口在发「数字市民」二维码，扫开是 404。</t>
+  </si>
+  <si>
+    <t>城市宣发与服务器没就绪并存。波间排窗口、扫码 404。</t>
   </si>
   <si>
     <t>Administrative</t>
@@ -1104,19 +1095,22 @@
     <t>开发、公职、银行与创业兄弟更容易相遇。</t>
   </si>
   <si>
-    <t>建设阵痛、岗位竞争和生活成本形成压力。</t>
+    <t>建设阵痛先到，岗位和生活成本变成波次压力。</t>
+  </si>
+  <si>
+    <t>玩法创作·PPT 广场</t>
   </si>
   <si>
     <t>hsr_open_2021</t>
   </si>
   <si>
-    <t>龙南进入高铁时代</t>
-  </si>
-  <si>
-    <t>2021年12月10日赣深高铁开通，龙南东站正式运营。</t>
-  </si>
-  <si>
-    <t>解锁龙南东站与返乡兄弟潮。</t>
+    <t>小卖部冰柜开始收点券</t>
+  </si>
+  <si>
+    <t>人从外地挤回来，柜台在冰棍旁边挂充值。抢的不是票，是包间和充电宝。</t>
+  </si>
+  <si>
+    <t>返乡潮进波间池。外地回来的兄弟更容易集合。</t>
   </si>
   <si>
     <t>Mechanical|Civil|Finance|Startup|Internet</t>
@@ -1125,16 +1119,13 @@
     <t>longnan_east</t>
   </si>
   <si>
-    <t>回乡过年和跨城工作的兄弟更容易重新集合。</t>
-  </si>
-  <si>
-    <t>客流高峰、抢票和接站混乱形成新敌潮。</t>
-  </si>
-  <si>
-    <t>龙南市人民政府·龙南东站正式运营</t>
-  </si>
-  <si>
-    <t>http://www.jxln.gov.cn/lnzf/c110699/202202/d5abc40cf11740a492181c764a313435.shtml</t>
+    <t>回乡过年和跨城加班的兄弟更容易重新集合。</t>
+  </si>
+  <si>
+    <t>抢的是包间和充电宝，人潮变成新敌潮。</t>
+  </si>
+  <si>
+    <t>玩法创作·点券冰柜</t>
   </si>
 </sst>
 </file>
@@ -1778,10 +1769,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2013,10 +2004,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2619,10 +2610,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2902,7 +2893,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>196</v>
       </c>
@@ -2934,7 +2925,7 @@
         <v>0.07</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>201</v>
       </c>
@@ -2966,7 +2957,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>207</v>
       </c>
@@ -2998,7 +2989,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>212</v>
       </c>
@@ -3030,7 +3021,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>218</v>
       </c>
@@ -3062,7 +3053,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>223</v>
       </c>
@@ -3094,7 +3085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>229</v>
       </c>
@@ -3794,16 +3785,16 @@
         <v>310</v>
       </c>
       <c r="Q5" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="R5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S5" t="s">
-        <v>312</v>
+        <v>24</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3859,7 +3850,7 @@
         <v>300</v>
       </c>
       <c r="R6" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="S6" t="s">
         <v>24</v>
@@ -3873,7 +3864,7 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C7">
         <v>2016</v>
@@ -3882,13 +3873,13 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
@@ -3897,10 +3888,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -3909,25 +3900,25 @@
         <v>207</v>
       </c>
       <c r="N7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q7" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="R7" t="s">
         <v>332</v>
       </c>
       <c r="S7" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3935,7 +3926,7 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C8">
         <v>2017</v>
@@ -3944,13 +3935,13 @@
         <v>40</v>
       </c>
       <c r="E8" t="s">
+        <v>334</v>
+      </c>
+      <c r="F8" t="s">
         <v>335</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>336</v>
-      </c>
-      <c r="G8" t="s">
-        <v>337</v>
       </c>
       <c r="H8" t="s">
         <v>31</v>
@@ -3959,10 +3950,10 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
+        <v>337</v>
+      </c>
+      <c r="K8" t="s">
         <v>338</v>
-      </c>
-      <c r="K8" t="s">
-        <v>339</v>
       </c>
       <c r="L8">
         <v>1.7</v>
@@ -3971,25 +3962,25 @@
         <v>212</v>
       </c>
       <c r="N8" t="s">
+        <v>339</v>
+      </c>
+      <c r="O8" t="s">
         <v>340</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>341</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>311</v>
+      </c>
+      <c r="R8" t="s">
         <v>342</v>
       </c>
-      <c r="Q8" t="s">
-        <v>331</v>
-      </c>
-      <c r="R8" t="s">
-        <v>343</v>
-      </c>
       <c r="S8" t="s">
-        <v>344</v>
+        <v>24</v>
       </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3997,7 +3988,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C9">
         <v>2019</v>
@@ -4006,13 +3997,13 @@
         <v>50</v>
       </c>
       <c r="E9" t="s">
+        <v>344</v>
+      </c>
+      <c r="F9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G9" t="s">
         <v>346</v>
-      </c>
-      <c r="F9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G9" t="s">
-        <v>348</v>
       </c>
       <c r="H9" t="s">
         <v>33</v>
@@ -4024,7 +4015,7 @@
         <v>317</v>
       </c>
       <c r="K9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L9">
         <v>1.9</v>
@@ -4036,22 +4027,22 @@
         <v>319</v>
       </c>
       <c r="O9" t="s">
+        <v>348</v>
+      </c>
+      <c r="P9" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>311</v>
+      </c>
+      <c r="R9" t="s">
         <v>350</v>
       </c>
-      <c r="P9" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>331</v>
-      </c>
-      <c r="R9" t="s">
-        <v>352</v>
-      </c>
       <c r="S9" t="s">
-        <v>353</v>
+        <v>24</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4059,7 +4050,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C10">
         <v>2020</v>
@@ -4068,13 +4059,13 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -4083,10 +4074,10 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="L10">
         <v>1.8</v>
@@ -4095,25 +4086,25 @@
         <v>223</v>
       </c>
       <c r="N10" t="s">
+        <v>357</v>
+      </c>
+      <c r="O10" t="s">
+        <v>358</v>
+      </c>
+      <c r="P10" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>311</v>
+      </c>
+      <c r="R10" t="s">
         <v>360</v>
       </c>
-      <c r="O10" t="s">
-        <v>361</v>
-      </c>
-      <c r="P10" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>226</v>
-      </c>
-      <c r="R10" t="s">
-        <v>311</v>
-      </c>
       <c r="S10" t="s">
-        <v>312</v>
+        <v>24</v>
       </c>
       <c r="T10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4121,7 +4112,7 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C11">
         <v>2021</v>
@@ -4130,13 +4121,13 @@
         <v>70</v>
       </c>
       <c r="E11" t="s">
+        <v>362</v>
+      </c>
+      <c r="F11" t="s">
+        <v>363</v>
+      </c>
+      <c r="G11" t="s">
         <v>364</v>
-      </c>
-      <c r="F11" t="s">
-        <v>365</v>
-      </c>
-      <c r="G11" t="s">
-        <v>366</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -4145,10 +4136,10 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -4157,25 +4148,25 @@
         <v>229</v>
       </c>
       <c r="N11" t="s">
+        <v>366</v>
+      </c>
+      <c r="O11" t="s">
+        <v>367</v>
+      </c>
+      <c r="P11" t="s">
         <v>368</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
+        <v>311</v>
+      </c>
+      <c r="R11" t="s">
         <v>369</v>
       </c>
-      <c r="P11" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>226</v>
-      </c>
-      <c r="R11" t="s">
-        <v>371</v>
-      </c>
       <c r="S11" t="s">
-        <v>372</v>
+        <v>24</v>
       </c>
       <c r="T11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
